--- a/output/StructureDefinition-MyPatient.xlsx
+++ b/output/StructureDefinition-MyPatient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T18:59:27+03:00</t>
+    <t>2026-03-22T11:14:06+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-MyPatient.xlsx
+++ b/output/StructureDefinition-MyPatient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-22T11:14:06+05:30</t>
+    <t>2026-03-22T13:21:26+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-MyPatient.xlsx
+++ b/output/StructureDefinition-MyPatient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-22T13:21:26+05:30</t>
+    <t>2026-03-25T09:53:08+03:00</t>
   </si>
   <si>
     <t>Publisher</t>
